--- a/MainTop/Остатки_бирки/остатки_бирки1.xlsx
+++ b/MainTop/Остатки_бирки/остатки_бирки1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\Остатки_бирки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7F3009-E24D-4264-95F5-85B1251C5805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D467496-1C7A-412C-809E-5C7127403BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Термобирки белые 30шт</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Термобирки Дисней мальчики</t>
   </si>
@@ -55,9 +52,6 @@
   </si>
   <si>
     <t>Термобирки Спанч боб, Соник ежик</t>
-  </si>
-  <si>
-    <t>Термобирки Леди Баг</t>
   </si>
   <si>
     <t>Термобирки Гарри Поттер</t>
@@ -394,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="1"/>
@@ -402,26 +396,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>150</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -429,86 +423,70 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
         <v>2</v>
       </c>
     </row>
